--- a/backend/data/users.xlsx
+++ b/backend/data/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,7 +430,7 @@
         <v>ahmadmehdi505@gmail.com</v>
       </c>
       <c r="D2" t="str">
-        <v>$2a$12$XJ5zSm9bwSz4l9bj4oxoQuuH1nGps4RW8tRGtt5iCF1nBQq6ufYUa</v>
+        <v>$2a$12$kivxPYnO1xrMl0DowdYa4OnGPKC1iZl8N/Pg32NUoKuLJmV/65edW</v>
       </c>
       <c r="E2" t="str">
         <v>admin</v>
@@ -519,9 +519,89 @@
         <v>2026-09-28T19:24:02.140Z</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>eb2442a3-8fc6-4524-baf5-b6a75ffd4757</v>
+      </c>
+      <c r="B7" t="str">
+        <v>zakarya</v>
+      </c>
+      <c r="C7" t="str">
+        <v>zakarya@gmail.com</v>
+      </c>
+      <c r="D7" t="str">
+        <v>$2a$12$D1wDfcdf/clSI7rlbDM3oe9hAsfLvYNNDmhliwR2SF9eBOkNzYBja</v>
+      </c>
+      <c r="E7" t="str">
+        <v>user</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-09-30T15:07:35.663Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>55941531-04e8-4237-8697-e5107b3902f4</v>
+      </c>
+      <c r="B8" t="str">
+        <v>zakarya</v>
+      </c>
+      <c r="C8" t="str">
+        <v>zakarya@gmail.com</v>
+      </c>
+      <c r="D8" t="str">
+        <v>$2a$12$2JpIRkRsrLiQuuOHV9IteedJNvk/IpwtyXpnz8hKVOpdkJLf2WIpC</v>
+      </c>
+      <c r="E8" t="str">
+        <v>user</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-09-30T15:07:36.460Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>00234a7c-a8e7-4c10-b09f-6b199501fe67</v>
+      </c>
+      <c r="B9" t="str">
+        <v>zakarya</v>
+      </c>
+      <c r="C9" t="str">
+        <v>zakarya@gmail.com</v>
+      </c>
+      <c r="D9" t="str">
+        <v>$2a$12$VXPdIFGmtmPAU71uMzTSWuqmn9krqguxexMGN4iC8PAFNvJViId/.</v>
+      </c>
+      <c r="E9" t="str">
+        <v>user</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-09-30T15:07:36.824Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>9dab1f1e-4208-438c-af86-32acada75933</v>
+      </c>
+      <c r="B10" t="str">
+        <v>zakarya</v>
+      </c>
+      <c r="C10" t="str">
+        <v>zakarya@gmail.com</v>
+      </c>
+      <c r="D10" t="str">
+        <v>$2a$12$rwBFXMBLq.F2bWBE9XWg0er/AKOPtmrer.JZvcWJ8BBI7QS8OOMC2</v>
+      </c>
+      <c r="E10" t="str">
+        <v>user</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-09-30T15:07:37.394Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
   </ignoredErrors>
 </worksheet>
 </file>